--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathwelt2.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathwelt2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{C58C8EB2-8A2D-4D46-8FCE-DBDB6388E82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B747286D-CADD-D248-99C8-17FF77809F64}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{C58C8EB2-8A2D-4D46-8FCE-DBDB6388E82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9393CF4C-904F-C640-8F67-1C792D02F082}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="620" windowWidth="26040" windowHeight="15880" xr2:uid="{2F4CF655-B5EA-DF41-8C7B-35EEE630F387}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7792" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7815" uniqueCount="158">
   <si>
     <t>Mathwelt 2 Themenbuch Sem 2.pdf</t>
   </si>
@@ -497,6 +497,39 @@
   </si>
   <si>
     <t>Einschätzung Potenzial</t>
+  </si>
+  <si>
+    <t>Proportionen</t>
+  </si>
+  <si>
+    <t>Gewicht und Volumen</t>
+  </si>
+  <si>
+    <t>Impressum und Nachweise</t>
+  </si>
+  <si>
+    <t>Keine Aufgaben</t>
+  </si>
+  <si>
+    <t>Symmetrien</t>
+  </si>
+  <si>
+    <t>Ornamente und Parkette</t>
+  </si>
+  <si>
+    <t>Dividieren</t>
+  </si>
+  <si>
+    <t>Projekte</t>
+  </si>
+  <si>
+    <t>hoch</t>
+  </si>
+  <si>
+    <t>Längen und Flächen</t>
+  </si>
+  <si>
+    <t>mittel</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1029,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1051,6 +1084,15 @@
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
@@ -1058,15 +1100,6 @@
         <b/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1109,15 +1142,15 @@
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{545C463E-64AF-CC4F-9487-061B939F1DD6}" name="Seite"/>
-    <tableColumn id="11" xr3:uid="{55D92858-1514-124F-931B-35AB6812A68D}" name="Schulbuchseite" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{55D92858-1514-124F-931B-35AB6812A68D}" name="Schulbuchseite" dataDxfId="5">
       <calculatedColumnFormula>Tabelle35[[#This Row],[Seite]]-0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{3632AA1D-6F08-A74D-B2B3-2B13FED65274}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{E76B3460-05CD-DB42-A5D1-2C8391BBE956}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{FC3CA071-D095-3A4E-8C0F-B50DD7C52819}" name="Summe Score" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{FC3CA071-D095-3A4E-8C0F-B50DD7C52819}" name="Summe Score" dataDxfId="4">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle1[Seite]=Q2)*Tabelle1[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3F5AE567-B9D8-C843-A23C-BE8281829A4A}" name="Thema" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{3F5AE567-B9D8-C843-A23C-BE8281829A4A}" name="Thema" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{4FB3D976-7239-9141-B95D-7EA2EC32984B}" name="Stufe BNE-Bezug"/>
     <tableColumn id="7" xr3:uid="{5E25E05D-80CD-C747-BE95-0D139FC4A6DB}" name="Reflexionstiefe"/>
     <tableColumn id="6" xr3:uid="{8B683C14-23DF-774E-B359-AE560C98BC80}" name="Einschätzung Potenzial"/>
@@ -1154,15 +1187,15 @@
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EFEF6C2C-B0B1-2843-AA1C-5C7D39A67449}" name="Seite"/>
-    <tableColumn id="11" xr3:uid="{C526E140-2A00-F74C-81F2-38F658F945F6}" name="Schulbuchseite" dataDxfId="4">
+    <tableColumn id="11" xr3:uid="{C526E140-2A00-F74C-81F2-38F658F945F6}" name="Schulbuchseite" dataDxfId="2">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Seite]]-0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{FE1851BE-DA2B-7D4C-817D-BB97B85D1027}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{3B7306AC-84D8-6C49-A623-55B412AEDAD4}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{6ACC64E6-9DD4-5449-83D1-76AF3288663B}" name="Summe Score" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{6ACC64E6-9DD4-5449-83D1-76AF3288663B}" name="Summe Score" dataDxfId="1">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle2[Seite]=Q2)*Tabelle2[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5D44ACE8-4F60-8446-B05D-C09E754EF7F6}" name="Thema" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{5D44ACE8-4F60-8446-B05D-C09E754EF7F6}" name="Thema" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{665070FD-7004-C94B-BBDC-9BA66202553B}" name="Stufe BNE-Bezug"/>
     <tableColumn id="7" xr3:uid="{0C1B2882-4968-2642-A534-80EBBDF131A9}" name="Reflexionstiefe"/>
     <tableColumn id="6" xr3:uid="{71A81B72-FCE5-6343-B6A7-BFC94E9A71F2}" name="Einschätzung Potenzial"/>
@@ -1606,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <f>COUNTIF(B$2:B$867, M2)</f>
+        <f t="shared" ref="N2:N33" si="0">COUNTIF(B$2:B$867, M2)</f>
         <v>22</v>
       </c>
       <c r="O2">
@@ -1620,17 +1653,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>2</v>
       </c>
-      <c r="S2">
-        <v>22</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2" s="2" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT((Tabelle1[Seite]=Q2)*Tabelle1[Score_Gewichtet])</f>
-        <v>10.049999999999997</v>
-      </c>
-      <c r="V2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1670,11 +1696,11 @@
         <v>3</v>
       </c>
       <c r="N3">
-        <f>COUNTIF(B$2:B$867, M3)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O66" si="0">RANK(N3, $N$2:$N$132)</f>
+        <f t="shared" ref="O3:O66" si="1">RANK(N3, $N$2:$N$132)</f>
         <v>47</v>
       </c>
       <c r="Q3">
@@ -1684,17 +1710,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>3</v>
       </c>
-      <c r="S3">
-        <v>7</v>
-      </c>
-      <c r="T3">
-        <v>47</v>
-      </c>
-      <c r="U3" s="2" cm="1">
-        <f t="array" ref="U3">SUMPRODUCT((Tabelle1[Seite]=Q3)*Tabelle1[Score_Gewichtet])</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="V3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1734,11 +1753,11 @@
         <v>4</v>
       </c>
       <c r="N4">
-        <f>COUNTIF(B$2:B$867, M4)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q4">
@@ -1748,17 +1767,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>4</v>
       </c>
-      <c r="S4">
-        <v>5</v>
-      </c>
-      <c r="T4">
-        <v>74</v>
-      </c>
-      <c r="U4" s="2" cm="1">
-        <f t="array" ref="U4">SUMPRODUCT((Tabelle1[Seite]=Q4)*Tabelle1[Score_Gewichtet])</f>
-        <v>1.2999999999999998</v>
-      </c>
-      <c r="V4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1798,11 +1810,11 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <f>COUNTIF(B$2:B$867, M5)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q5">
@@ -1812,17 +1824,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>5</v>
       </c>
-      <c r="S5">
-        <v>20</v>
-      </c>
-      <c r="T5">
-        <v>2</v>
-      </c>
-      <c r="U5" s="2" cm="1">
-        <f t="array" ref="U5">SUMPRODUCT((Tabelle1[Seite]=Q5)*Tabelle1[Score_Gewichtet])</f>
-        <v>55.2</v>
-      </c>
-      <c r="V5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1862,11 +1867,11 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <f>COUNTIF(B$2:B$867, M6)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q6">
@@ -1926,11 +1931,11 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <f>COUNTIF(B$2:B$867, M7)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q7">
@@ -1990,11 +1995,11 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <f>COUNTIF(B$2:B$867, M8)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q8">
@@ -2054,11 +2059,11 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <f>COUNTIF(B$2:B$867, M9)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="O9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q9">
@@ -2118,11 +2123,11 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <f>COUNTIF(B$2:B$867, M10)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="O10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="Q10">
@@ -2142,7 +2147,9 @@
         <f t="array" ref="U10">SUMPRODUCT((Tabelle1[Seite]=Q10)*Tabelle1[Score_Gewichtet])</f>
         <v>19.850000000000001</v>
       </c>
-      <c r="V10" s="2"/>
+      <c r="V10" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -2182,11 +2189,11 @@
         <v>11</v>
       </c>
       <c r="N11">
-        <f>COUNTIF(B$2:B$867, M11)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q11">
@@ -2246,11 +2253,11 @@
         <v>12</v>
       </c>
       <c r="N12">
-        <f>COUNTIF(B$2:B$867, M12)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q12">
@@ -2310,11 +2317,11 @@
         <v>14</v>
       </c>
       <c r="N13">
-        <f>COUNTIF(B$2:B$867, M13)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="O13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q13">
@@ -2374,11 +2381,11 @@
         <v>15</v>
       </c>
       <c r="N14">
-        <f>COUNTIF(B$2:B$867, M14)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q14">
@@ -2438,11 +2445,11 @@
         <v>16</v>
       </c>
       <c r="N15">
-        <f>COUNTIF(B$2:B$867, M15)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q15">
@@ -2502,11 +2509,11 @@
         <v>17</v>
       </c>
       <c r="N16">
-        <f>COUNTIF(B$2:B$867, M16)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="O16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="Q16">
@@ -2566,11 +2573,11 @@
         <v>18</v>
       </c>
       <c r="N17">
-        <f>COUNTIF(B$2:B$867, M17)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q17">
@@ -2630,11 +2637,11 @@
         <v>19</v>
       </c>
       <c r="N18">
-        <f>COUNTIF(B$2:B$867, M18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="Q18">
@@ -2694,11 +2701,11 @@
         <v>20</v>
       </c>
       <c r="N19">
-        <f>COUNTIF(B$2:B$867, M19)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="O19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="Q19">
@@ -2758,11 +2765,11 @@
         <v>21</v>
       </c>
       <c r="N20">
-        <f>COUNTIF(B$2:B$867, M20)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q20">
@@ -2822,11 +2829,11 @@
         <v>22</v>
       </c>
       <c r="N21">
-        <f>COUNTIF(B$2:B$867, M21)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q21">
@@ -2886,11 +2893,11 @@
         <v>23</v>
       </c>
       <c r="N22">
-        <f>COUNTIF(B$2:B$867, M22)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q22">
@@ -2950,11 +2957,11 @@
         <v>24</v>
       </c>
       <c r="N23">
-        <f>COUNTIF(B$2:B$867, M23)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="O23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="Q23">
@@ -3014,11 +3021,11 @@
         <v>25</v>
       </c>
       <c r="N24">
-        <f>COUNTIF(B$2:B$867, M24)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q24">
@@ -3078,11 +3085,11 @@
         <v>26</v>
       </c>
       <c r="N25">
-        <f>COUNTIF(B$2:B$867, M25)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q25">
@@ -3142,11 +3149,11 @@
         <v>27</v>
       </c>
       <c r="N26">
-        <f>COUNTIF(B$2:B$867, M26)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q26">
@@ -3206,11 +3213,11 @@
         <v>28</v>
       </c>
       <c r="N27">
-        <f>COUNTIF(B$2:B$867, M27)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="O27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q27">
@@ -3270,11 +3277,11 @@
         <v>29</v>
       </c>
       <c r="N28">
-        <f>COUNTIF(B$2:B$867, M28)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q28">
@@ -3334,11 +3341,11 @@
         <v>30</v>
       </c>
       <c r="N29">
-        <f>COUNTIF(B$2:B$867, M29)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q29">
@@ -3398,11 +3405,11 @@
         <v>31</v>
       </c>
       <c r="N30">
-        <f>COUNTIF(B$2:B$867, M30)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q30">
@@ -3462,11 +3469,11 @@
         <v>32</v>
       </c>
       <c r="N31">
-        <f>COUNTIF(B$2:B$867, M31)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="O31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Q31">
@@ -3526,11 +3533,11 @@
         <v>33</v>
       </c>
       <c r="N32">
-        <f>COUNTIF(B$2:B$867, M32)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q32">
@@ -3552,7 +3559,7 @@
       </c>
       <c r="V32" s="2"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -3590,11 +3597,11 @@
         <v>34</v>
       </c>
       <c r="N33">
-        <f>COUNTIF(B$2:B$867, M33)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q33">
@@ -3616,7 +3623,7 @@
       </c>
       <c r="V33" s="2"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>126</v>
       </c>
@@ -3654,11 +3661,11 @@
         <v>35</v>
       </c>
       <c r="N34">
-        <f>COUNTIF(B$2:B$867, M34)</f>
+        <f t="shared" ref="N34:N65" si="2">COUNTIF(B$2:B$867, M34)</f>
         <v>4</v>
       </c>
       <c r="O34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q34">
@@ -3680,7 +3687,7 @@
       </c>
       <c r="V34" s="2"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>126</v>
       </c>
@@ -3718,11 +3725,11 @@
         <v>36</v>
       </c>
       <c r="N35">
-        <f>COUNTIF(B$2:B$867, M35)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q35">
@@ -3744,7 +3751,7 @@
       </c>
       <c r="V35" s="2"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>126</v>
       </c>
@@ -3782,11 +3789,11 @@
         <v>37</v>
       </c>
       <c r="N36">
-        <f>COUNTIF(B$2:B$867, M36)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="O36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q36">
@@ -3808,7 +3815,7 @@
       </c>
       <c r="V36" s="2"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>126</v>
       </c>
@@ -3846,11 +3853,11 @@
         <v>38</v>
       </c>
       <c r="N37">
-        <f>COUNTIF(B$2:B$867, M37)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q37">
@@ -3872,7 +3879,7 @@
       </c>
       <c r="V37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -3910,11 +3917,11 @@
         <v>39</v>
       </c>
       <c r="N38">
-        <f>COUNTIF(B$2:B$867, M38)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q38">
@@ -3936,7 +3943,7 @@
       </c>
       <c r="V38" s="2"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -3974,11 +3981,11 @@
         <v>40</v>
       </c>
       <c r="N39">
-        <f>COUNTIF(B$2:B$867, M39)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q39">
@@ -4000,7 +4007,7 @@
       </c>
       <c r="V39" s="2"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>126</v>
       </c>
@@ -4038,11 +4045,11 @@
         <v>41</v>
       </c>
       <c r="N40">
-        <f>COUNTIF(B$2:B$867, M40)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q40">
@@ -4064,7 +4071,7 @@
       </c>
       <c r="V40" s="2"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -4102,11 +4109,11 @@
         <v>42</v>
       </c>
       <c r="N41">
-        <f>COUNTIF(B$2:B$867, M41)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="O41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q41">
@@ -4128,7 +4135,7 @@
       </c>
       <c r="V41" s="2"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -4166,11 +4173,11 @@
         <v>43</v>
       </c>
       <c r="N42">
-        <f>COUNTIF(B$2:B$867, M42)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="O42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q42">
@@ -4192,7 +4199,7 @@
       </c>
       <c r="V42" s="2"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -4230,11 +4237,11 @@
         <v>44</v>
       </c>
       <c r="N43">
-        <f>COUNTIF(B$2:B$867, M43)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="O43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q43">
@@ -4256,7 +4263,7 @@
       </c>
       <c r="V43" s="2"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -4294,11 +4301,11 @@
         <v>45</v>
       </c>
       <c r="N44">
-        <f>COUNTIF(B$2:B$867, M44)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="O44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q44">
@@ -4320,7 +4327,7 @@
       </c>
       <c r="V44" s="2"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -4358,11 +4365,11 @@
         <v>46</v>
       </c>
       <c r="N45">
-        <f>COUNTIF(B$2:B$867, M45)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="Q45">
@@ -4384,7 +4391,7 @@
       </c>
       <c r="V45" s="2"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>126</v>
       </c>
@@ -4422,11 +4429,11 @@
         <v>47</v>
       </c>
       <c r="N46">
-        <f>COUNTIF(B$2:B$867, M46)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="O46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q46">
@@ -4448,7 +4455,7 @@
       </c>
       <c r="V46" s="2"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>126</v>
       </c>
@@ -4486,11 +4493,11 @@
         <v>48</v>
       </c>
       <c r="N47">
-        <f>COUNTIF(B$2:B$867, M47)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="Q47">
@@ -4512,7 +4519,7 @@
       </c>
       <c r="V47" s="2"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>126</v>
       </c>
@@ -4550,11 +4557,11 @@
         <v>49</v>
       </c>
       <c r="N48">
-        <f>COUNTIF(B$2:B$867, M48)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q48">
@@ -4574,7 +4581,18 @@
         <f t="array" ref="U48">SUMPRODUCT((Tabelle1[Seite]=Q48)*Tabelle1[Score_Gewichtet])</f>
         <v>3.2000000000000006</v>
       </c>
-      <c r="V48" s="2"/>
+      <c r="V48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -4614,11 +4632,11 @@
         <v>50</v>
       </c>
       <c r="N49">
-        <f>COUNTIF(B$2:B$867, M49)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="O49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q49">
@@ -4678,11 +4696,11 @@
         <v>51</v>
       </c>
       <c r="N50">
-        <f>COUNTIF(B$2:B$867, M50)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="O50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Q50">
@@ -4742,11 +4760,11 @@
         <v>52</v>
       </c>
       <c r="N51">
-        <f>COUNTIF(B$2:B$867, M51)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="O51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q51">
@@ -4806,11 +4824,11 @@
         <v>53</v>
       </c>
       <c r="N52">
-        <f>COUNTIF(B$2:B$867, M52)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="Q52">
@@ -4870,11 +4888,11 @@
         <v>54</v>
       </c>
       <c r="N53">
-        <f>COUNTIF(B$2:B$867, M53)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q53">
@@ -4934,11 +4952,11 @@
         <v>55</v>
       </c>
       <c r="N54">
-        <f>COUNTIF(B$2:B$867, M54)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="O54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q54">
@@ -4998,11 +5016,11 @@
         <v>56</v>
       </c>
       <c r="N55">
-        <f>COUNTIF(B$2:B$867, M55)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q55">
@@ -5062,11 +5080,11 @@
         <v>57</v>
       </c>
       <c r="N56">
-        <f>COUNTIF(B$2:B$867, M56)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="O56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q56">
@@ -5126,11 +5144,11 @@
         <v>58</v>
       </c>
       <c r="N57">
-        <f>COUNTIF(B$2:B$867, M57)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="Q57">
@@ -5190,11 +5208,11 @@
         <v>59</v>
       </c>
       <c r="N58">
-        <f>COUNTIF(B$2:B$867, M58)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q58">
@@ -5254,11 +5272,11 @@
         <v>60</v>
       </c>
       <c r="N59">
-        <f>COUNTIF(B$2:B$867, M59)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="O59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="Q59">
@@ -5318,11 +5336,11 @@
         <v>61</v>
       </c>
       <c r="N60">
-        <f>COUNTIF(B$2:B$867, M60)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="O60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="Q60">
@@ -5382,11 +5400,11 @@
         <v>62</v>
       </c>
       <c r="N61">
-        <f>COUNTIF(B$2:B$867, M61)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="O61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q61">
@@ -5446,11 +5464,11 @@
         <v>63</v>
       </c>
       <c r="N62">
-        <f>COUNTIF(B$2:B$867, M62)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="Q62">
@@ -5510,11 +5528,11 @@
         <v>64</v>
       </c>
       <c r="N63">
-        <f>COUNTIF(B$2:B$867, M63)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="Q63">
@@ -5574,11 +5592,11 @@
         <v>65</v>
       </c>
       <c r="N64">
-        <f>COUNTIF(B$2:B$867, M64)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q64">
@@ -5638,11 +5656,11 @@
         <v>66</v>
       </c>
       <c r="N65">
-        <f>COUNTIF(B$2:B$867, M65)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="Q65">
@@ -5702,11 +5720,11 @@
         <v>67</v>
       </c>
       <c r="N66">
-        <f>COUNTIF(B$2:B$867, M66)</f>
+        <f t="shared" ref="N66:N97" si="3">COUNTIF(B$2:B$867, M66)</f>
         <v>3</v>
       </c>
       <c r="O66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="Q66">
@@ -5766,11 +5784,11 @@
         <v>68</v>
       </c>
       <c r="N67">
-        <f>COUNTIF(B$2:B$867, M67)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O130" si="1">RANK(N67, $N$2:$N$132)</f>
+        <f t="shared" ref="O67:O130" si="4">RANK(N67, $N$2:$N$132)</f>
         <v>35</v>
       </c>
       <c r="Q67">
@@ -5830,11 +5848,11 @@
         <v>69</v>
       </c>
       <c r="N68">
-        <f>COUNTIF(B$2:B$867, M68)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="O68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q68">
@@ -5894,11 +5912,11 @@
         <v>70</v>
       </c>
       <c r="N69">
-        <f>COUNTIF(B$2:B$867, M69)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="O69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="Q69">
@@ -5958,11 +5976,11 @@
         <v>71</v>
       </c>
       <c r="N70">
-        <f>COUNTIF(B$2:B$867, M70)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>115</v>
       </c>
       <c r="Q70">
@@ -6022,11 +6040,11 @@
         <v>72</v>
       </c>
       <c r="N71">
-        <f>COUNTIF(B$2:B$867, M71)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q71">
@@ -6086,11 +6104,11 @@
         <v>73</v>
       </c>
       <c r="N72">
-        <f>COUNTIF(B$2:B$867, M72)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q72">
@@ -6150,11 +6168,11 @@
         <v>75</v>
       </c>
       <c r="N73">
-        <f>COUNTIF(B$2:B$867, M73)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q73">
@@ -6214,11 +6232,11 @@
         <v>76</v>
       </c>
       <c r="N74">
-        <f>COUNTIF(B$2:B$867, M74)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q74">
@@ -6278,11 +6296,11 @@
         <v>77</v>
       </c>
       <c r="N75">
-        <f>COUNTIF(B$2:B$867, M75)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q75">
@@ -6342,11 +6360,11 @@
         <v>79</v>
       </c>
       <c r="N76">
-        <f>COUNTIF(B$2:B$867, M76)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q76">
@@ -6406,11 +6424,11 @@
         <v>80</v>
       </c>
       <c r="N77">
-        <f>COUNTIF(B$2:B$867, M77)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>115</v>
       </c>
       <c r="Q77">
@@ -6470,11 +6488,11 @@
         <v>81</v>
       </c>
       <c r="N78">
-        <f>COUNTIF(B$2:B$867, M78)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q78">
@@ -6534,11 +6552,11 @@
         <v>82</v>
       </c>
       <c r="N79">
-        <f>COUNTIF(B$2:B$867, M79)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="O79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q79">
@@ -6598,11 +6616,11 @@
         <v>83</v>
       </c>
       <c r="N80">
-        <f>COUNTIF(B$2:B$867, M80)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q80">
@@ -6624,7 +6642,7 @@
       </c>
       <c r="V80" s="2"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>126</v>
       </c>
@@ -6662,11 +6680,11 @@
         <v>84</v>
       </c>
       <c r="N81">
-        <f>COUNTIF(B$2:B$867, M81)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="Q81">
@@ -6686,9 +6704,20 @@
         <f t="array" ref="U81">SUMPRODUCT((Tabelle1[Seite]=Q81)*Tabelle1[Score_Gewichtet])</f>
         <v>1.5</v>
       </c>
-      <c r="V81" s="2"/>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V81" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="W81">
+        <v>2</v>
+      </c>
+      <c r="X81">
+        <v>3</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>126</v>
       </c>
@@ -6726,11 +6755,11 @@
         <v>85</v>
       </c>
       <c r="N82">
-        <f>COUNTIF(B$2:B$867, M82)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="Q82">
@@ -6752,7 +6781,7 @@
       </c>
       <c r="V82" s="2"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>126</v>
       </c>
@@ -6790,11 +6819,11 @@
         <v>86</v>
       </c>
       <c r="N83">
-        <f>COUNTIF(B$2:B$867, M83)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="O83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q83">
@@ -6816,7 +6845,7 @@
       </c>
       <c r="V83" s="2"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>126</v>
       </c>
@@ -6854,11 +6883,11 @@
         <v>87</v>
       </c>
       <c r="N84">
-        <f>COUNTIF(B$2:B$867, M84)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q84">
@@ -6880,7 +6909,7 @@
       </c>
       <c r="V84" s="2"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>126</v>
       </c>
@@ -6918,11 +6947,11 @@
         <v>88</v>
       </c>
       <c r="N85">
-        <f>COUNTIF(B$2:B$867, M85)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="Q85">
@@ -6944,7 +6973,7 @@
       </c>
       <c r="V85" s="2"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>126</v>
       </c>
@@ -6982,11 +7011,11 @@
         <v>89</v>
       </c>
       <c r="N86">
-        <f>COUNTIF(B$2:B$867, M86)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="O86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="Q86">
@@ -7008,7 +7037,7 @@
       </c>
       <c r="V86" s="2"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>126</v>
       </c>
@@ -7046,11 +7075,11 @@
         <v>90</v>
       </c>
       <c r="N87">
-        <f>COUNTIF(B$2:B$867, M87)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="Q87">
@@ -7072,7 +7101,7 @@
       </c>
       <c r="V87" s="2"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>126</v>
       </c>
@@ -7110,11 +7139,11 @@
         <v>91</v>
       </c>
       <c r="N88">
-        <f>COUNTIF(B$2:B$867, M88)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="O88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q88">
@@ -7136,7 +7165,7 @@
       </c>
       <c r="V88" s="2"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>126</v>
       </c>
@@ -7174,11 +7203,11 @@
         <v>92</v>
       </c>
       <c r="N89">
-        <f>COUNTIF(B$2:B$867, M89)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q89">
@@ -7200,7 +7229,7 @@
       </c>
       <c r="V89" s="2"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -7238,11 +7267,11 @@
         <v>93</v>
       </c>
       <c r="N90">
-        <f>COUNTIF(B$2:B$867, M90)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="Q90">
@@ -7264,7 +7293,7 @@
       </c>
       <c r="V90" s="2"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -7302,11 +7331,11 @@
         <v>94</v>
       </c>
       <c r="N91">
-        <f>COUNTIF(B$2:B$867, M91)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q91">
@@ -7328,7 +7357,7 @@
       </c>
       <c r="V91" s="2"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>126</v>
       </c>
@@ -7366,11 +7395,11 @@
         <v>95</v>
       </c>
       <c r="N92">
-        <f>COUNTIF(B$2:B$867, M92)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="Q92">
@@ -7392,7 +7421,7 @@
       </c>
       <c r="V92" s="2"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>126</v>
       </c>
@@ -7430,11 +7459,11 @@
         <v>96</v>
       </c>
       <c r="N93">
-        <f>COUNTIF(B$2:B$867, M93)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q93">
@@ -7456,7 +7485,7 @@
       </c>
       <c r="V93" s="2"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>126</v>
       </c>
@@ -7494,11 +7523,11 @@
         <v>97</v>
       </c>
       <c r="N94">
-        <f>COUNTIF(B$2:B$867, M94)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q94">
@@ -7520,7 +7549,7 @@
       </c>
       <c r="V94" s="2"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>126</v>
       </c>
@@ -7558,11 +7587,11 @@
         <v>98</v>
       </c>
       <c r="N95">
-        <f>COUNTIF(B$2:B$867, M95)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q95">
@@ -7584,7 +7613,7 @@
       </c>
       <c r="V95" s="2"/>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>126</v>
       </c>
@@ -7622,11 +7651,11 @@
         <v>99</v>
       </c>
       <c r="N96">
-        <f>COUNTIF(B$2:B$867, M96)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="O96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q96">
@@ -7686,11 +7715,11 @@
         <v>100</v>
       </c>
       <c r="N97">
-        <f>COUNTIF(B$2:B$867, M97)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="Q97">
@@ -7750,11 +7779,11 @@
         <v>101</v>
       </c>
       <c r="N98">
-        <f>COUNTIF(B$2:B$867, M98)</f>
+        <f t="shared" ref="N98:N129" si="5">COUNTIF(B$2:B$867, M98)</f>
         <v>8</v>
       </c>
       <c r="O98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q98">
@@ -7814,11 +7843,11 @@
         <v>102</v>
       </c>
       <c r="N99">
-        <f>COUNTIF(B$2:B$867, M99)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="O99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q99">
@@ -7838,7 +7867,9 @@
         <f t="array" ref="U99">SUMPRODUCT((Tabelle1[Seite]=Q99)*Tabelle1[Score_Gewichtet])</f>
         <v>19.349999999999998</v>
       </c>
-      <c r="V99" s="2"/>
+      <c r="V99" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
@@ -7878,11 +7909,11 @@
         <v>103</v>
       </c>
       <c r="N100">
-        <f>COUNTIF(B$2:B$867, M100)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q100">
@@ -7942,11 +7973,11 @@
         <v>104</v>
       </c>
       <c r="N101">
-        <f>COUNTIF(B$2:B$867, M101)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q101">
@@ -8006,11 +8037,11 @@
         <v>105</v>
       </c>
       <c r="N102">
-        <f>COUNTIF(B$2:B$867, M102)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>115</v>
       </c>
       <c r="Q102">
@@ -8070,11 +8101,11 @@
         <v>106</v>
       </c>
       <c r="N103">
-        <f>COUNTIF(B$2:B$867, M103)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="O103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="Q103">
@@ -8134,11 +8165,11 @@
         <v>108</v>
       </c>
       <c r="N104">
-        <f>COUNTIF(B$2:B$867, M104)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q104">
@@ -8198,11 +8229,11 @@
         <v>110</v>
       </c>
       <c r="N105">
-        <f>COUNTIF(B$2:B$867, M105)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q105">
@@ -8262,11 +8293,11 @@
         <v>111</v>
       </c>
       <c r="N106">
-        <f>COUNTIF(B$2:B$867, M106)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q106">
@@ -8326,11 +8357,11 @@
         <v>112</v>
       </c>
       <c r="N107">
-        <f>COUNTIF(B$2:B$867, M107)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="O107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q107">
@@ -8390,11 +8421,11 @@
         <v>113</v>
       </c>
       <c r="N108">
-        <f>COUNTIF(B$2:B$867, M108)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q108">
@@ -8454,11 +8485,11 @@
         <v>114</v>
       </c>
       <c r="N109">
-        <f>COUNTIF(B$2:B$867, M109)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q109">
@@ -8518,11 +8549,11 @@
         <v>115</v>
       </c>
       <c r="N110">
-        <f>COUNTIF(B$2:B$867, M110)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="O110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q110">
@@ -8582,11 +8613,11 @@
         <v>116</v>
       </c>
       <c r="N111">
-        <f>COUNTIF(B$2:B$867, M111)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q111">
@@ -8646,11 +8677,11 @@
         <v>117</v>
       </c>
       <c r="N112">
-        <f>COUNTIF(B$2:B$867, M112)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q112">
@@ -8710,11 +8741,11 @@
         <v>120</v>
       </c>
       <c r="N113">
-        <f>COUNTIF(B$2:B$867, M113)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q113">
@@ -8774,11 +8805,11 @@
         <v>121</v>
       </c>
       <c r="N114">
-        <f>COUNTIF(B$2:B$867, M114)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q114">
@@ -8838,11 +8869,11 @@
         <v>122</v>
       </c>
       <c r="N115">
-        <f>COUNTIF(B$2:B$867, M115)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q115">
@@ -8902,11 +8933,11 @@
         <v>123</v>
       </c>
       <c r="N116">
-        <f>COUNTIF(B$2:B$867, M116)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q116">
@@ -8966,11 +8997,11 @@
         <v>124</v>
       </c>
       <c r="N117">
-        <f>COUNTIF(B$2:B$867, M117)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="O117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q117">
@@ -9030,11 +9061,11 @@
         <v>125</v>
       </c>
       <c r="N118">
-        <f>COUNTIF(B$2:B$867, M118)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q118">
@@ -9094,11 +9125,11 @@
         <v>126</v>
       </c>
       <c r="N119">
-        <f>COUNTIF(B$2:B$867, M119)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="Q119">
@@ -9158,11 +9189,11 @@
         <v>127</v>
       </c>
       <c r="N120">
-        <f>COUNTIF(B$2:B$867, M120)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q120">
@@ -9222,11 +9253,11 @@
         <v>128</v>
       </c>
       <c r="N121">
-        <f>COUNTIF(B$2:B$867, M121)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="O121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="Q121">
@@ -9286,11 +9317,11 @@
         <v>129</v>
       </c>
       <c r="N122">
-        <f>COUNTIF(B$2:B$867, M122)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q122">
@@ -9350,11 +9381,11 @@
         <v>131</v>
       </c>
       <c r="N123">
-        <f>COUNTIF(B$2:B$867, M123)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="O123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="Q123">
@@ -9414,11 +9445,11 @@
         <v>132</v>
       </c>
       <c r="N124">
-        <f>COUNTIF(B$2:B$867, M124)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="O124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="Q124">
@@ -9478,11 +9509,11 @@
         <v>133</v>
       </c>
       <c r="N125">
-        <f>COUNTIF(B$2:B$867, M125)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="O125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="Q125">
@@ -9542,11 +9573,11 @@
         <v>134</v>
       </c>
       <c r="N126">
-        <f>COUNTIF(B$2:B$867, M126)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="Q126">
@@ -9606,11 +9637,11 @@
         <v>135</v>
       </c>
       <c r="N127">
-        <f>COUNTIF(B$2:B$867, M127)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q127">
@@ -9670,11 +9701,11 @@
         <v>136</v>
       </c>
       <c r="N128">
-        <f>COUNTIF(B$2:B$867, M128)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Q128">
@@ -9684,17 +9715,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>136</v>
       </c>
-      <c r="S128">
-        <v>8</v>
-      </c>
-      <c r="T128">
-        <v>35</v>
-      </c>
-      <c r="U128" s="2" cm="1">
-        <f t="array" ref="U128">SUMPRODUCT((Tabelle1[Seite]=Q128)*Tabelle1[Score_Gewichtet])</f>
-        <v>3.6</v>
-      </c>
-      <c r="V128" s="2"/>
+      <c r="U128" s="2"/>
+      <c r="V128" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
@@ -9734,11 +9758,11 @@
         <v>137</v>
       </c>
       <c r="N129">
-        <f>COUNTIF(B$2:B$867, M129)</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="O129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q129">
@@ -9748,17 +9772,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>137</v>
       </c>
-      <c r="S129">
-        <v>14</v>
-      </c>
-      <c r="T129">
-        <v>5</v>
-      </c>
-      <c r="U129" s="2" cm="1">
-        <f t="array" ref="U129">SUMPRODUCT((Tabelle1[Seite]=Q129)*Tabelle1[Score_Gewichtet])</f>
-        <v>12.399999999999999</v>
-      </c>
-      <c r="V129" s="2"/>
+      <c r="U129" s="2"/>
+      <c r="V129" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
@@ -9798,11 +9815,11 @@
         <v>138</v>
       </c>
       <c r="N130">
-        <f>COUNTIF(B$2:B$867, M130)</f>
+        <f t="shared" ref="N130:N161" si="6">COUNTIF(B$2:B$867, M130)</f>
         <v>9</v>
       </c>
       <c r="O130">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q130">
@@ -9812,17 +9829,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>138</v>
       </c>
-      <c r="S130">
-        <v>9</v>
-      </c>
-      <c r="T130">
-        <v>24</v>
-      </c>
-      <c r="U130" s="2" cm="1">
-        <f t="array" ref="U130">SUMPRODUCT((Tabelle1[Seite]=Q130)*Tabelle1[Score_Gewichtet])</f>
-        <v>36.85</v>
-      </c>
-      <c r="V130" s="2"/>
+      <c r="U130" s="2"/>
+      <c r="V130" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
@@ -9862,11 +9872,11 @@
         <v>139</v>
       </c>
       <c r="N131">
-        <f>COUNTIF(B$2:B$867, M131)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O131">
-        <f t="shared" ref="O131:O132" si="2">RANK(N131, $N$2:$N$132)</f>
+        <f t="shared" ref="O131:O132" si="7">RANK(N131, $N$2:$N$132)</f>
         <v>10</v>
       </c>
       <c r="Q131">
@@ -9876,17 +9886,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>139</v>
       </c>
-      <c r="S131">
-        <v>12</v>
-      </c>
-      <c r="T131">
-        <v>10</v>
-      </c>
-      <c r="U131" s="2" cm="1">
-        <f t="array" ref="U131">SUMPRODUCT((Tabelle1[Seite]=Q131)*Tabelle1[Score_Gewichtet])</f>
-        <v>54.7</v>
-      </c>
-      <c r="V131" s="2"/>
+      <c r="U131" s="2"/>
+      <c r="V131" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
@@ -9926,11 +9929,11 @@
         <v>140</v>
       </c>
       <c r="N132">
-        <f>COUNTIF(B$2:B$867, M132)</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="O132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="Q132">
@@ -9940,17 +9943,10 @@
         <f>Tabelle35[[#This Row],[Seite]]-0</f>
         <v>140</v>
       </c>
-      <c r="S132">
-        <v>9</v>
-      </c>
-      <c r="T132">
-        <v>24</v>
-      </c>
-      <c r="U132" s="2" cm="1">
-        <f t="array" ref="U132">SUMPRODUCT((Tabelle1[Seite]=Q132)*Tabelle1[Score_Gewichtet])</f>
-        <v>22.25</v>
-      </c>
-      <c r="V132" s="2"/>
+      <c r="U132" s="2"/>
+      <c r="V132" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
@@ -10111,9 +10107,9 @@
         <f>COUNTIF(Tabelle35[Stufe BNE-Bezug],U136)</f>
         <v>0</v>
       </c>
-      <c r="X136" s="3" t="e">
+      <c r="X136" s="3">
         <f>W136/W$140</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.2">
@@ -10159,11 +10155,11 @@
       </c>
       <c r="W137">
         <f>COUNTIF(Tabelle35[Stufe BNE-Bezug],U137)</f>
-        <v>0</v>
-      </c>
-      <c r="X137" s="3" t="e">
+        <v>2</v>
+      </c>
+      <c r="X137" s="3">
         <f>W137/W$140</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.2">
@@ -10211,9 +10207,9 @@
         <f>COUNTIF(Tabelle35[Stufe BNE-Bezug],U138)</f>
         <v>0</v>
       </c>
-      <c r="X138" s="3" t="e">
+      <c r="X138" s="3">
         <f>W138/W$140</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.2">
@@ -10261,9 +10257,9 @@
         <f>COUNTIF(Tabelle35[Stufe BNE-Bezug],U139)</f>
         <v>0</v>
       </c>
-      <c r="X139" s="3" t="e">
+      <c r="X139" s="3">
         <f>W139/W$140</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.2">
@@ -10305,7 +10301,7 @@
       </c>
       <c r="W140">
         <f>SUM(W136:W139)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.2">
@@ -35754,6 +35750,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="U2:U132">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="W2:W132">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -35761,16 +35767,6 @@
         <cfvo type="max"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U132">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -35897,7 +35893,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <f>COUNTIF(B$2:B$1069, M2)</f>
+        <f t="shared" ref="N2:N33" si="0">COUNTIF(B$2:B$1069, M2)</f>
         <v>1</v>
       </c>
       <c r="O2">
@@ -35961,11 +35957,11 @@
         <v>2</v>
       </c>
       <c r="N3">
-        <f>COUNTIF(B$2:B$1069, M3)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O66" si="0">RANK(N3, $N$2:$N$139)</f>
+        <f t="shared" ref="O3:O66" si="1">RANK(N3, $N$2:$N$139)</f>
         <v>2</v>
       </c>
       <c r="Q3">
@@ -36025,11 +36021,11 @@
         <v>3</v>
       </c>
       <c r="N4">
-        <f>COUNTIF(B$2:B$1069, M4)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="Q4">
@@ -36089,11 +36085,11 @@
         <v>4</v>
       </c>
       <c r="N5">
-        <f>COUNTIF(B$2:B$1069, M5)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q5">
@@ -36153,11 +36149,11 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <f>COUNTIF(B$2:B$1069, M6)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q6">
@@ -36217,11 +36213,11 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <f>COUNTIF(B$2:B$1069, M7)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q7">
@@ -36281,11 +36277,11 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <f>COUNTIF(B$2:B$1069, M8)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="Q8">
@@ -36345,11 +36341,11 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <f>COUNTIF(B$2:B$1069, M9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q9">
@@ -36409,11 +36405,11 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <f>COUNTIF(B$2:B$1069, M10)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="O10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q10">
@@ -36473,11 +36469,11 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <f>COUNTIF(B$2:B$1069, M11)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="O11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q11">
@@ -36537,11 +36533,11 @@
         <v>11</v>
       </c>
       <c r="N12">
-        <f>COUNTIF(B$2:B$1069, M12)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q12">
@@ -36601,11 +36597,11 @@
         <v>12</v>
       </c>
       <c r="N13">
-        <f>COUNTIF(B$2:B$1069, M13)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q13">
@@ -36665,11 +36661,11 @@
         <v>13</v>
       </c>
       <c r="N14">
-        <f>COUNTIF(B$2:B$1069, M14)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q14">
@@ -36729,11 +36725,11 @@
         <v>14</v>
       </c>
       <c r="N15">
-        <f>COUNTIF(B$2:B$1069, M15)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="O15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q15">
@@ -36793,11 +36789,11 @@
         <v>15</v>
       </c>
       <c r="N16">
-        <f>COUNTIF(B$2:B$1069, M16)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="O16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="Q16">
@@ -36857,11 +36853,11 @@
         <v>16</v>
       </c>
       <c r="N17">
-        <f>COUNTIF(B$2:B$1069, M17)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="O17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q17">
@@ -36921,11 +36917,11 @@
         <v>17</v>
       </c>
       <c r="N18">
-        <f>COUNTIF(B$2:B$1069, M18)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="O18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q18">
@@ -36985,11 +36981,11 @@
         <v>18</v>
       </c>
       <c r="N19">
-        <f>COUNTIF(B$2:B$1069, M19)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="O19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q19">
@@ -37049,11 +37045,11 @@
         <v>19</v>
       </c>
       <c r="N20">
-        <f>COUNTIF(B$2:B$1069, M20)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q20">
@@ -37113,11 +37109,11 @@
         <v>20</v>
       </c>
       <c r="N21">
-        <f>COUNTIF(B$2:B$1069, M21)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="Q21">
@@ -37177,11 +37173,11 @@
         <v>21</v>
       </c>
       <c r="N22">
-        <f>COUNTIF(B$2:B$1069, M22)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="Q22">
@@ -37241,11 +37237,11 @@
         <v>22</v>
       </c>
       <c r="N23">
-        <f>COUNTIF(B$2:B$1069, M23)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="Q23">
@@ -37305,11 +37301,11 @@
         <v>23</v>
       </c>
       <c r="N24">
-        <f>COUNTIF(B$2:B$1069, M24)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="O24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q24">
@@ -37369,11 +37365,11 @@
         <v>24</v>
       </c>
       <c r="N25">
-        <f>COUNTIF(B$2:B$1069, M25)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="O25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q25">
@@ -37433,11 +37429,11 @@
         <v>25</v>
       </c>
       <c r="N26">
-        <f>COUNTIF(B$2:B$1069, M26)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="O26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q26">
@@ -37497,11 +37493,11 @@
         <v>26</v>
       </c>
       <c r="N27">
-        <f>COUNTIF(B$2:B$1069, M27)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="Q27">
@@ -37561,11 +37557,11 @@
         <v>27</v>
       </c>
       <c r="N28">
-        <f>COUNTIF(B$2:B$1069, M28)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="O28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="Q28">
@@ -37625,11 +37621,11 @@
         <v>28</v>
       </c>
       <c r="N29">
-        <f>COUNTIF(B$2:B$1069, M29)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="O29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q29">
@@ -37689,11 +37685,11 @@
         <v>29</v>
       </c>
       <c r="N30">
-        <f>COUNTIF(B$2:B$1069, M30)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="O30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q30">
@@ -37753,11 +37749,11 @@
         <v>30</v>
       </c>
       <c r="N31">
-        <f>COUNTIF(B$2:B$1069, M31)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="O31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="Q31">
@@ -37817,11 +37813,11 @@
         <v>31</v>
       </c>
       <c r="N32">
-        <f>COUNTIF(B$2:B$1069, M32)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="O32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q32">
@@ -37881,11 +37877,11 @@
         <v>32</v>
       </c>
       <c r="N33">
-        <f>COUNTIF(B$2:B$1069, M33)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="O33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q33">
@@ -37945,11 +37941,11 @@
         <v>33</v>
       </c>
       <c r="N34">
-        <f>COUNTIF(B$2:B$1069, M34)</f>
+        <f t="shared" ref="N34:N65" si="2">COUNTIF(B$2:B$1069, M34)</f>
         <v>3</v>
       </c>
       <c r="O34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q34">
@@ -38009,11 +38005,11 @@
         <v>34</v>
       </c>
       <c r="N35">
-        <f>COUNTIF(B$2:B$1069, M35)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q35">
@@ -38073,11 +38069,11 @@
         <v>35</v>
       </c>
       <c r="N36">
-        <f>COUNTIF(B$2:B$1069, M36)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="O36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q36">
@@ -38137,11 +38133,11 @@
         <v>36</v>
       </c>
       <c r="N37">
-        <f>COUNTIF(B$2:B$1069, M37)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q37">
@@ -38201,11 +38197,11 @@
         <v>37</v>
       </c>
       <c r="N38">
-        <f>COUNTIF(B$2:B$1069, M38)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="O38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="Q38">
@@ -38265,11 +38261,11 @@
         <v>38</v>
       </c>
       <c r="N39">
-        <f>COUNTIF(B$2:B$1069, M39)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="O39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="Q39">
@@ -38289,7 +38285,9 @@
         <f t="array" ref="U39">SUMPRODUCT((Tabelle2[Seite]=Q39)*Tabelle2[Score_Gewichtet])</f>
         <v>32.9</v>
       </c>
-      <c r="V39" s="2"/>
+      <c r="V39" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -38329,11 +38327,11 @@
         <v>39</v>
       </c>
       <c r="N40">
-        <f>COUNTIF(B$2:B$1069, M40)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q40">
@@ -38393,11 +38391,11 @@
         <v>40</v>
       </c>
       <c r="N41">
-        <f>COUNTIF(B$2:B$1069, M41)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="O41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="Q41">
@@ -38417,7 +38415,9 @@
         <f t="array" ref="U41">SUMPRODUCT((Tabelle2[Seite]=Q41)*Tabelle2[Score_Gewichtet])</f>
         <v>30.7</v>
       </c>
-      <c r="V41" s="2"/>
+      <c r="V41" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -38457,11 +38457,11 @@
         <v>41</v>
       </c>
       <c r="N42">
-        <f>COUNTIF(B$2:B$1069, M42)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="Q42">
@@ -38521,11 +38521,11 @@
         <v>42</v>
       </c>
       <c r="N43">
-        <f>COUNTIF(B$2:B$1069, M43)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="O43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="Q43">
@@ -38585,11 +38585,11 @@
         <v>43</v>
       </c>
       <c r="N44">
-        <f>COUNTIF(B$2:B$1069, M44)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="Q44">
@@ -38649,11 +38649,11 @@
         <v>44</v>
       </c>
       <c r="N45">
-        <f>COUNTIF(B$2:B$1069, M45)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q45">
@@ -38713,11 +38713,11 @@
         <v>45</v>
       </c>
       <c r="N46">
-        <f>COUNTIF(B$2:B$1069, M46)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="Q46">
@@ -38777,11 +38777,11 @@
         <v>46</v>
       </c>
       <c r="N47">
-        <f>COUNTIF(B$2:B$1069, M47)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="O47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="Q47">
@@ -38841,11 +38841,11 @@
         <v>47</v>
       </c>
       <c r="N48">
-        <f>COUNTIF(B$2:B$1069, M48)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="Q48">
@@ -38905,11 +38905,11 @@
         <v>48</v>
       </c>
       <c r="N49">
-        <f>COUNTIF(B$2:B$1069, M49)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q49">
@@ -38969,11 +38969,11 @@
         <v>49</v>
       </c>
       <c r="N50">
-        <f>COUNTIF(B$2:B$1069, M50)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q50">
@@ -39033,11 +39033,11 @@
         <v>50</v>
       </c>
       <c r="N51">
-        <f>COUNTIF(B$2:B$1069, M51)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="Q51">
@@ -39097,11 +39097,11 @@
         <v>51</v>
       </c>
       <c r="N52">
-        <f>COUNTIF(B$2:B$1069, M52)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="O52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="Q52">
@@ -39161,11 +39161,11 @@
         <v>52</v>
       </c>
       <c r="N53">
-        <f>COUNTIF(B$2:B$1069, M53)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="O53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q53">
@@ -39225,11 +39225,11 @@
         <v>53</v>
       </c>
       <c r="N54">
-        <f>COUNTIF(B$2:B$1069, M54)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="O54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="Q54">
@@ -39289,11 +39289,11 @@
         <v>54</v>
       </c>
       <c r="N55">
-        <f>COUNTIF(B$2:B$1069, M55)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q55">
@@ -39353,11 +39353,11 @@
         <v>55</v>
       </c>
       <c r="N56">
-        <f>COUNTIF(B$2:B$1069, M56)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q56">
@@ -39417,11 +39417,11 @@
         <v>56</v>
       </c>
       <c r="N57">
-        <f>COUNTIF(B$2:B$1069, M57)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="O57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q57">
@@ -39481,11 +39481,11 @@
         <v>57</v>
       </c>
       <c r="N58">
-        <f>COUNTIF(B$2:B$1069, M58)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="O58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q58">
@@ -39545,11 +39545,11 @@
         <v>58</v>
       </c>
       <c r="N59">
-        <f>COUNTIF(B$2:B$1069, M59)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="O59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="Q59">
@@ -39609,11 +39609,11 @@
         <v>59</v>
       </c>
       <c r="N60">
-        <f>COUNTIF(B$2:B$1069, M60)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="O60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="Q60">
@@ -39673,11 +39673,11 @@
         <v>60</v>
       </c>
       <c r="N61">
-        <f>COUNTIF(B$2:B$1069, M61)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="O61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="Q61">
@@ -39737,11 +39737,11 @@
         <v>61</v>
       </c>
       <c r="N62">
-        <f>COUNTIF(B$2:B$1069, M62)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="O62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="Q62">
@@ -39801,11 +39801,11 @@
         <v>62</v>
       </c>
       <c r="N63">
-        <f>COUNTIF(B$2:B$1069, M63)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="O63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q63">
@@ -39865,11 +39865,11 @@
         <v>63</v>
       </c>
       <c r="N64">
-        <f>COUNTIF(B$2:B$1069, M64)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="O64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="Q64">
@@ -39929,11 +39929,11 @@
         <v>64</v>
       </c>
       <c r="N65">
-        <f>COUNTIF(B$2:B$1069, M65)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="O65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q65">
@@ -39993,11 +39993,11 @@
         <v>65</v>
       </c>
       <c r="N66">
-        <f>COUNTIF(B$2:B$1069, M66)</f>
+        <f t="shared" ref="N66:N97" si="3">COUNTIF(B$2:B$1069, M66)</f>
         <v>3</v>
       </c>
       <c r="O66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="Q66">
@@ -40057,11 +40057,11 @@
         <v>66</v>
       </c>
       <c r="N67">
-        <f>COUNTIF(B$2:B$1069, M67)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O130" si="1">RANK(N67, $N$2:$N$139)</f>
+        <f t="shared" ref="O67:O130" si="4">RANK(N67, $N$2:$N$139)</f>
         <v>65</v>
       </c>
       <c r="Q67">
@@ -40121,11 +40121,11 @@
         <v>67</v>
       </c>
       <c r="N68">
-        <f>COUNTIF(B$2:B$1069, M68)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="Q68">
@@ -40185,11 +40185,11 @@
         <v>68</v>
       </c>
       <c r="N69">
-        <f>COUNTIF(B$2:B$1069, M69)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q69">
@@ -40249,11 +40249,11 @@
         <v>69</v>
       </c>
       <c r="N70">
-        <f>COUNTIF(B$2:B$1069, M70)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q70">
@@ -40313,11 +40313,11 @@
         <v>70</v>
       </c>
       <c r="N71">
-        <f>COUNTIF(B$2:B$1069, M71)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q71">
@@ -40377,11 +40377,11 @@
         <v>71</v>
       </c>
       <c r="N72">
-        <f>COUNTIF(B$2:B$1069, M72)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="Q72">
@@ -40441,11 +40441,11 @@
         <v>72</v>
       </c>
       <c r="N73">
-        <f>COUNTIF(B$2:B$1069, M73)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q73">
@@ -40505,11 +40505,11 @@
         <v>73</v>
       </c>
       <c r="N74">
-        <f>COUNTIF(B$2:B$1069, M74)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q74">
@@ -40569,11 +40569,11 @@
         <v>74</v>
       </c>
       <c r="N75">
-        <f>COUNTIF(B$2:B$1069, M75)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="O75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="Q75">
@@ -40633,11 +40633,11 @@
         <v>75</v>
       </c>
       <c r="N76">
-        <f>COUNTIF(B$2:B$1069, M76)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="Q76">
@@ -40697,11 +40697,11 @@
         <v>76</v>
       </c>
       <c r="N77">
-        <f>COUNTIF(B$2:B$1069, M77)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="Q77">
@@ -40761,11 +40761,11 @@
         <v>77</v>
       </c>
       <c r="N78">
-        <f>COUNTIF(B$2:B$1069, M78)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="O78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q78">
@@ -40825,11 +40825,11 @@
         <v>78</v>
       </c>
       <c r="N79">
-        <f>COUNTIF(B$2:B$1069, M79)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q79">
@@ -40889,11 +40889,11 @@
         <v>79</v>
       </c>
       <c r="N80">
-        <f>COUNTIF(B$2:B$1069, M80)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q80">
@@ -40953,11 +40953,11 @@
         <v>80</v>
       </c>
       <c r="N81">
-        <f>COUNTIF(B$2:B$1069, M81)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q81">
@@ -41017,11 +41017,11 @@
         <v>81</v>
       </c>
       <c r="N82">
-        <f>COUNTIF(B$2:B$1069, M82)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q82">
@@ -41081,11 +41081,11 @@
         <v>82</v>
       </c>
       <c r="N83">
-        <f>COUNTIF(B$2:B$1069, M83)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="Q83">
@@ -41145,11 +41145,11 @@
         <v>83</v>
       </c>
       <c r="N84">
-        <f>COUNTIF(B$2:B$1069, M84)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q84">
@@ -41209,11 +41209,11 @@
         <v>84</v>
       </c>
       <c r="N85">
-        <f>COUNTIF(B$2:B$1069, M85)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q85">
@@ -41273,11 +41273,11 @@
         <v>85</v>
       </c>
       <c r="N86">
-        <f>COUNTIF(B$2:B$1069, M86)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="O86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="Q86">
@@ -41337,11 +41337,11 @@
         <v>86</v>
       </c>
       <c r="N87">
-        <f>COUNTIF(B$2:B$1069, M87)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="Q87">
@@ -41401,11 +41401,11 @@
         <v>87</v>
       </c>
       <c r="N88">
-        <f>COUNTIF(B$2:B$1069, M88)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q88">
@@ -41465,11 +41465,11 @@
         <v>88</v>
       </c>
       <c r="N89">
-        <f>COUNTIF(B$2:B$1069, M89)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q89">
@@ -41529,11 +41529,11 @@
         <v>89</v>
       </c>
       <c r="N90">
-        <f>COUNTIF(B$2:B$1069, M90)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="O90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q90">
@@ -41593,11 +41593,11 @@
         <v>90</v>
       </c>
       <c r="N91">
-        <f>COUNTIF(B$2:B$1069, M91)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="Q91">
@@ -41657,11 +41657,11 @@
         <v>91</v>
       </c>
       <c r="N92">
-        <f>COUNTIF(B$2:B$1069, M92)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q92">
@@ -41721,11 +41721,11 @@
         <v>92</v>
       </c>
       <c r="N93">
-        <f>COUNTIF(B$2:B$1069, M93)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q93">
@@ -41785,11 +41785,11 @@
         <v>93</v>
       </c>
       <c r="N94">
-        <f>COUNTIF(B$2:B$1069, M94)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q94">
@@ -41849,11 +41849,11 @@
         <v>94</v>
       </c>
       <c r="N95">
-        <f>COUNTIF(B$2:B$1069, M95)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="O95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q95">
@@ -41913,11 +41913,11 @@
         <v>95</v>
       </c>
       <c r="N96">
-        <f>COUNTIF(B$2:B$1069, M96)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q96">
@@ -41977,11 +41977,11 @@
         <v>96</v>
       </c>
       <c r="N97">
-        <f>COUNTIF(B$2:B$1069, M97)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="O97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="Q97">
@@ -42041,11 +42041,11 @@
         <v>97</v>
       </c>
       <c r="N98">
-        <f>COUNTIF(B$2:B$1069, M98)</f>
+        <f t="shared" ref="N98:N129" si="5">COUNTIF(B$2:B$1069, M98)</f>
         <v>3</v>
       </c>
       <c r="O98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q98">
@@ -42105,11 +42105,11 @@
         <v>98</v>
       </c>
       <c r="N99">
-        <f>COUNTIF(B$2:B$1069, M99)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q99">
@@ -42169,11 +42169,11 @@
         <v>99</v>
       </c>
       <c r="N100">
-        <f>COUNTIF(B$2:B$1069, M100)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="O100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q100">
@@ -42233,11 +42233,11 @@
         <v>100</v>
       </c>
       <c r="N101">
-        <f>COUNTIF(B$2:B$1069, M101)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q101">
@@ -42297,11 +42297,11 @@
         <v>101</v>
       </c>
       <c r="N102">
-        <f>COUNTIF(B$2:B$1069, M102)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="O102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="Q102">
@@ -42361,11 +42361,11 @@
         <v>102</v>
       </c>
       <c r="N103">
-        <f>COUNTIF(B$2:B$1069, M103)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="O103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q103">
@@ -42425,11 +42425,11 @@
         <v>103</v>
       </c>
       <c r="N104">
-        <f>COUNTIF(B$2:B$1069, M104)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="Q104">
@@ -42489,11 +42489,11 @@
         <v>104</v>
       </c>
       <c r="N105">
-        <f>COUNTIF(B$2:B$1069, M105)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q105">
@@ -42553,11 +42553,11 @@
         <v>105</v>
       </c>
       <c r="N106">
-        <f>COUNTIF(B$2:B$1069, M106)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="Q106">
@@ -42617,11 +42617,11 @@
         <v>106</v>
       </c>
       <c r="N107">
-        <f>COUNTIF(B$2:B$1069, M107)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q107">
@@ -42681,11 +42681,11 @@
         <v>107</v>
       </c>
       <c r="N108">
-        <f>COUNTIF(B$2:B$1069, M108)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="O108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q108">
@@ -42745,11 +42745,11 @@
         <v>108</v>
       </c>
       <c r="N109">
-        <f>COUNTIF(B$2:B$1069, M109)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="Q109">
@@ -42809,11 +42809,11 @@
         <v>109</v>
       </c>
       <c r="N110">
-        <f>COUNTIF(B$2:B$1069, M110)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q110">
@@ -42873,11 +42873,11 @@
         <v>110</v>
       </c>
       <c r="N111">
-        <f>COUNTIF(B$2:B$1069, M111)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q111">
@@ -42897,7 +42897,9 @@
         <f t="array" ref="U111">SUMPRODUCT((Tabelle2[Seite]=Q111)*Tabelle2[Score_Gewichtet])</f>
         <v>29.349999999999998</v>
       </c>
-      <c r="V111" s="2"/>
+      <c r="V111" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
@@ -42937,11 +42939,11 @@
         <v>111</v>
       </c>
       <c r="N112">
-        <f>COUNTIF(B$2:B$1069, M112)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q112">
@@ -43001,11 +43003,11 @@
         <v>112</v>
       </c>
       <c r="N113">
-        <f>COUNTIF(B$2:B$1069, M113)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q113">
@@ -43065,11 +43067,11 @@
         <v>113</v>
       </c>
       <c r="N114">
-        <f>COUNTIF(B$2:B$1069, M114)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q114">
@@ -43129,11 +43131,11 @@
         <v>114</v>
       </c>
       <c r="N115">
-        <f>COUNTIF(B$2:B$1069, M115)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="O115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="Q115">
@@ -43193,11 +43195,11 @@
         <v>115</v>
       </c>
       <c r="N116">
-        <f>COUNTIF(B$2:B$1069, M116)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="O116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q116">
@@ -43257,11 +43259,11 @@
         <v>116</v>
       </c>
       <c r="N117">
-        <f>COUNTIF(B$2:B$1069, M117)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="O117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="Q117">
@@ -43321,11 +43323,11 @@
         <v>117</v>
       </c>
       <c r="N118">
-        <f>COUNTIF(B$2:B$1069, M118)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="O118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="Q118">
@@ -43385,11 +43387,11 @@
         <v>118</v>
       </c>
       <c r="N119">
-        <f>COUNTIF(B$2:B$1069, M119)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="O119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="Q119">
@@ -43449,11 +43451,11 @@
         <v>119</v>
       </c>
       <c r="N120">
-        <f>COUNTIF(B$2:B$1069, M120)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q120">
@@ -43513,11 +43515,11 @@
         <v>120</v>
       </c>
       <c r="N121">
-        <f>COUNTIF(B$2:B$1069, M121)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q121">
@@ -43577,11 +43579,11 @@
         <v>121</v>
       </c>
       <c r="N122">
-        <f>COUNTIF(B$2:B$1069, M122)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="O122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="Q122">
@@ -43641,11 +43643,11 @@
         <v>122</v>
       </c>
       <c r="N123">
-        <f>COUNTIF(B$2:B$1069, M123)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="O123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="Q123">
@@ -43705,11 +43707,11 @@
         <v>123</v>
       </c>
       <c r="N124">
-        <f>COUNTIF(B$2:B$1069, M124)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="Q124">
@@ -43769,11 +43771,11 @@
         <v>124</v>
       </c>
       <c r="N125">
-        <f>COUNTIF(B$2:B$1069, M125)</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="O125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="Q125">
@@ -43833,11 +43835,11 @@
         <v>125</v>
       </c>
       <c r="N126">
-        <f>COUNTIF(B$2:B$1069, M126)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="O126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="Q126">
@@ -43897,11 +43899,11 @@
         <v>126</v>
       </c>
       <c r="N127">
-        <f>COUNTIF(B$2:B$1069, M127)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="Q127">
@@ -43961,11 +43963,11 @@
         <v>127</v>
       </c>
       <c r="N128">
-        <f>COUNTIF(B$2:B$1069, M128)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="O128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q128">
@@ -44025,11 +44027,11 @@
         <v>128</v>
       </c>
       <c r="N129">
-        <f>COUNTIF(B$2:B$1069, M129)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="O129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="Q129">
@@ -44089,11 +44091,11 @@
         <v>129</v>
       </c>
       <c r="N130">
-        <f>COUNTIF(B$2:B$1069, M130)</f>
+        <f t="shared" ref="N130:N161" si="6">COUNTIF(B$2:B$1069, M130)</f>
         <v>12</v>
       </c>
       <c r="O130">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="Q130">
@@ -44153,11 +44155,11 @@
         <v>130</v>
       </c>
       <c r="N131">
-        <f>COUNTIF(B$2:B$1069, M131)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="O131">
-        <f t="shared" ref="O131:O139" si="2">RANK(N131, $N$2:$N$139)</f>
+        <f t="shared" ref="O131:O139" si="7">RANK(N131, $N$2:$N$139)</f>
         <v>31</v>
       </c>
       <c r="Q131">
@@ -44217,11 +44219,11 @@
         <v>131</v>
       </c>
       <c r="N132">
-        <f>COUNTIF(B$2:B$1069, M132)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="O132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="Q132">
@@ -44281,11 +44283,11 @@
         <v>132</v>
       </c>
       <c r="N133">
-        <f>COUNTIF(B$2:B$1069, M133)</f>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="O133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="Q133">
@@ -44305,7 +44307,9 @@
         <f t="array" ref="U133">SUMPRODUCT((Tabelle2[Seite]=Q133)*Tabelle2[Score_Gewichtet])</f>
         <v>27.55</v>
       </c>
-      <c r="V133" s="2"/>
+      <c r="V133" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
@@ -44345,11 +44349,11 @@
         <v>133</v>
       </c>
       <c r="N134">
-        <f>COUNTIF(B$2:B$1069, M134)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="O134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="Q134">
@@ -44409,11 +44413,11 @@
         <v>134</v>
       </c>
       <c r="N135">
-        <f>COUNTIF(B$2:B$1069, M135)</f>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="O135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="Q135">
@@ -44433,7 +44437,9 @@
         <f t="array" ref="U135">SUMPRODUCT((Tabelle2[Seite]=Q135)*Tabelle2[Score_Gewichtet])</f>
         <v>27.049999999999997</v>
       </c>
-      <c r="V135" s="2"/>
+      <c r="V135" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
@@ -44473,11 +44479,11 @@
         <v>135</v>
       </c>
       <c r="N136">
-        <f>COUNTIF(B$2:B$1069, M136)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="O136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="Q136">
@@ -44537,11 +44543,11 @@
         <v>136</v>
       </c>
       <c r="N137">
-        <f>COUNTIF(B$2:B$1069, M137)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="O137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>89</v>
       </c>
       <c r="Q137">
@@ -44551,17 +44557,10 @@
         <f>Tabelle3[[#This Row],[Seite]]-0</f>
         <v>136</v>
       </c>
-      <c r="S137">
-        <v>5</v>
-      </c>
-      <c r="T137">
-        <v>89</v>
-      </c>
-      <c r="U137" s="2" cm="1">
-        <f t="array" ref="U137">SUMPRODUCT((Tabelle2[Seite]=Q137)*Tabelle2[Score_Gewichtet])</f>
-        <v>31.6</v>
-      </c>
-      <c r="V137" s="2"/>
+      <c r="U137" s="2"/>
+      <c r="V137" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
@@ -44601,11 +44600,11 @@
         <v>137</v>
       </c>
       <c r="N138">
-        <f>COUNTIF(B$2:B$1069, M138)</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="O138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>56</v>
       </c>
       <c r="Q138">
@@ -44615,17 +44614,10 @@
         <f>Tabelle3[[#This Row],[Seite]]-0</f>
         <v>137</v>
       </c>
-      <c r="S138">
-        <v>8</v>
-      </c>
-      <c r="T138">
-        <v>56</v>
-      </c>
-      <c r="U138" s="2" cm="1">
-        <f t="array" ref="U138">SUMPRODUCT((Tabelle2[Seite]=Q138)*Tabelle2[Score_Gewichtet])</f>
-        <v>57.400000000000006</v>
-      </c>
-      <c r="V138" s="2"/>
+      <c r="U138" s="2"/>
+      <c r="V138" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
@@ -44665,11 +44657,11 @@
         <v>138</v>
       </c>
       <c r="N139">
-        <f>COUNTIF(B$2:B$1069, M139)</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="O139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="Q139">
@@ -44679,17 +44671,10 @@
         <f>Tabelle3[[#This Row],[Seite]]-0</f>
         <v>138</v>
       </c>
-      <c r="S139">
-        <v>13</v>
-      </c>
-      <c r="T139">
-        <v>15</v>
-      </c>
-      <c r="U139" s="2" cm="1">
-        <f t="array" ref="U139">SUMPRODUCT((Tabelle2[Seite]=Q139)*Tabelle2[Score_Gewichtet])</f>
-        <v>41.699999999999996</v>
-      </c>
-      <c r="V139" s="2"/>
+      <c r="U139" s="2"/>
+      <c r="V139" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
@@ -77305,6 +77290,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="U2:U139">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="W2:W139">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -77315,16 +77310,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U139">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>

--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathwelt2.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathwelt2.xlsx
@@ -8,26 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMac/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="747" documentId="8_{C58C8EB2-8A2D-4D46-8FCE-DBDB6388E82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16196DA2-C73C-504F-9D90-34E63D82C9BE}"/>
+  <xr:revisionPtr revIDLastSave="772" documentId="8_{C58C8EB2-8A2D-4D46-8FCE-DBDB6388E82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A54C120-F2CE-2B4C-9492-721580930B21}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="620" windowWidth="26040" windowHeight="15880" activeTab="1" xr2:uid="{2F4CF655-B5EA-DF41-8C7B-35EEE630F387}"/>
+    <workbookView xWindow="500" yWindow="620" windowWidth="26040" windowHeight="15880" xr2:uid="{2F4CF655-B5EA-DF41-8C7B-35EEE630F387}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle 1 MW2Sem1" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle 2 MW2Sem2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">'Tabelle 2 MW2Sem2'!$T$150</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">'Tabelle 2 MW2Sem2'!$T$151</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">'Tabelle 2 MW2Sem2'!$T$152</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">'Tabelle 2 MW2Sem2'!$U$150,'Tabelle 2 MW2Sem2'!$W$150:$X$150</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">'Tabelle 2 MW2Sem2'!$U$151,'Tabelle 2 MW2Sem2'!$W$151:$X$151</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">'Tabelle 2 MW2Sem2'!$U$152,'Tabelle 2 MW2Sem2'!$W$152:$X$152</definedName>
-    <definedName name="_xlchart.v2.6" hidden="1">'Tabelle 2 MW2Sem2'!$T$150:$T$152</definedName>
-    <definedName name="_xlchart.v2.7" hidden="1">'Tabelle 2 MW2Sem2'!$U$150:$U$152</definedName>
-    <definedName name="_xlchart.v2.8" hidden="1">'Tabelle 2 MW2Sem2'!$W$150:$W$152</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">'Tabelle 2 MW2Sem2'!$X$150:$X$152</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7921" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7923" uniqueCount="235">
   <si>
     <t>Mathwelt 2 Themenbuch Sem 2.pdf</t>
   </si>
@@ -1786,6 +1774,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1315406288"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1991,7 +1980,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>19</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>29</c:v>
@@ -2055,7 +2044,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.14074074074074075</c:v>
+                  <c:v>0.79259259259259263</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.21481481481481482</c:v>
@@ -2247,6 +2236,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1867443456"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -14824,7 +14814,7 @@
         <v>3</v>
       </c>
       <c r="V150" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="W150">
         <f>COUNTIF(Tabelle35[Einschätzung Potenzial],U150)</f>
@@ -14873,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="V151" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="W151">
         <f>COUNTIF(Tabelle35[Einschätzung Potenzial],U151)</f>
@@ -14922,7 +14912,7 @@
         <v>1</v>
       </c>
       <c r="V152" t="s">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="W152">
         <f>COUNTIF(Tabelle35[Einschätzung Potenzial],U152)</f>
@@ -14966,6 +14956,20 @@
       </c>
       <c r="K153">
         <v>0.5</v>
+      </c>
+      <c r="U153">
+        <v>0</v>
+      </c>
+      <c r="V153" t="s">
+        <v>177</v>
+      </c>
+      <c r="W153">
+        <f>COUNTIF(Tabelle35[Einschätzung Potenzial],U153)</f>
+        <v>99</v>
+      </c>
+      <c r="X153" s="3">
+        <f t="shared" ref="X153" si="10">W153/W$141</f>
+        <v>0.77952755905511806</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.2">
@@ -40006,7 +40010,7 @@
   <dimension ref="A1:AB1069"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>115</v>
       </c>
@@ -40077,7 +40081,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -40147,12 +40151,11 @@
       <c r="X2">
         <v>1</v>
       </c>
-      <c r="Z2">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -40221,12 +40224,11 @@
       <c r="X3">
         <v>1</v>
       </c>
-      <c r="Z3">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -40295,12 +40297,11 @@
       <c r="X4">
         <v>1</v>
       </c>
-      <c r="Z4">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -40369,12 +40370,11 @@
       <c r="X5">
         <v>1</v>
       </c>
-      <c r="Z5">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -40443,12 +40443,11 @@
       <c r="X6">
         <v>1</v>
       </c>
-      <c r="Z6">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -40517,12 +40516,11 @@
       <c r="X7">
         <v>1</v>
       </c>
-      <c r="Z7">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -40591,12 +40589,11 @@
       <c r="X8">
         <v>1</v>
       </c>
-      <c r="Z8">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -40665,12 +40662,11 @@
       <c r="X9">
         <v>1</v>
       </c>
-      <c r="Z9">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -40739,12 +40735,11 @@
       <c r="X10">
         <v>1</v>
       </c>
-      <c r="Z10">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -40813,12 +40808,11 @@
       <c r="X11">
         <v>1</v>
       </c>
-      <c r="Z11">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -40884,12 +40878,14 @@
       <c r="W12">
         <v>0</v>
       </c>
-      <c r="Z12">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -40958,12 +40954,11 @@
       <c r="X13">
         <v>1</v>
       </c>
-      <c r="Z13">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -41032,12 +41027,11 @@
       <c r="X14">
         <v>1</v>
       </c>
-      <c r="Z14">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -41106,12 +41100,11 @@
       <c r="X15">
         <v>1</v>
       </c>
-      <c r="Z15">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -41177,9 +41170,11 @@
       <c r="W16">
         <v>0</v>
       </c>
-      <c r="Z16">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -41248,9 +41243,11 @@
       <c r="W17">
         <v>0</v>
       </c>
-      <c r="Z17">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -41319,9 +41316,11 @@
       <c r="W18">
         <v>0</v>
       </c>
-      <c r="Z18">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -41398,10 +41397,6 @@
       <c r="Y19">
         <v>3</v>
       </c>
-      <c r="Z19">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA19" t="s">
         <v>186</v>
       </c>
@@ -41472,9 +41467,11 @@
       <c r="W20">
         <v>0</v>
       </c>
-      <c r="Z20">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -41543,9 +41540,11 @@
       <c r="W21">
         <v>0</v>
       </c>
-      <c r="Z21">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -41622,10 +41621,6 @@
       <c r="Y22">
         <v>3</v>
       </c>
-      <c r="Z22">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -41693,9 +41688,11 @@
       <c r="W23">
         <v>0</v>
       </c>
-      <c r="Z23">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -41764,9 +41761,11 @@
       <c r="W24">
         <v>0</v>
       </c>
-      <c r="Z24">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -41835,9 +41834,11 @@
       <c r="W25">
         <v>0</v>
       </c>
-      <c r="Z25">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -41906,9 +41907,11 @@
       <c r="W26">
         <v>0</v>
       </c>
-      <c r="Z26">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -41977,9 +41980,11 @@
       <c r="W27">
         <v>0</v>
       </c>
-      <c r="Z27">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -42048,9 +42053,11 @@
       <c r="W28">
         <v>0</v>
       </c>
-      <c r="Z28">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -42127,10 +42134,6 @@
       <c r="Y29">
         <v>3</v>
       </c>
-      <c r="Z29">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA29" t="s">
         <v>190</v>
       </c>
@@ -42209,10 +42212,6 @@
       <c r="Y30">
         <v>3</v>
       </c>
-      <c r="Z30">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA30" t="s">
         <v>192</v>
       </c>
@@ -42291,10 +42290,6 @@
       <c r="Y31">
         <v>3</v>
       </c>
-      <c r="Z31">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
       <c r="AA31" t="s">
         <v>190</v>
       </c>
@@ -42371,10 +42366,6 @@
       <c r="Y32">
         <v>1</v>
       </c>
-      <c r="Z32">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -42442,9 +42433,11 @@
       <c r="W33">
         <v>0</v>
       </c>
-      <c r="Z33">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.2">
@@ -42513,9 +42506,11 @@
       <c r="W34">
         <v>0</v>
       </c>
-      <c r="Z34">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.2">
@@ -42592,10 +42587,6 @@
       <c r="Y35">
         <v>2</v>
       </c>
-      <c r="Z35">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
       <c r="AA35" t="s">
         <v>195</v>
       </c>
@@ -42674,10 +42665,6 @@
       <c r="Y36">
         <v>1</v>
       </c>
-      <c r="Z36">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -42745,9 +42732,11 @@
       <c r="W37">
         <v>0</v>
       </c>
-      <c r="Z37">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.2">
@@ -42824,10 +42813,6 @@
       <c r="Y38">
         <v>2</v>
       </c>
-      <c r="Z38">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -42903,10 +42888,6 @@
       <c r="Y39">
         <v>2</v>
       </c>
-      <c r="Z39">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA39" t="s">
         <v>198</v>
       </c>
@@ -42985,10 +42966,6 @@
       <c r="Y40">
         <v>2</v>
       </c>
-      <c r="Z40">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA40" t="s">
         <v>199</v>
       </c>
@@ -43067,10 +43044,6 @@
       <c r="Y41">
         <v>3</v>
       </c>
-      <c r="Z41">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA41" t="s">
         <v>201</v>
       </c>
@@ -43144,9 +43117,11 @@
       <c r="W42">
         <v>0</v>
       </c>
-      <c r="Z42">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.2">
@@ -43215,9 +43190,11 @@
       <c r="W43">
         <v>0</v>
       </c>
-      <c r="Z43">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.2">
@@ -43286,9 +43263,11 @@
       <c r="W44">
         <v>0</v>
       </c>
-      <c r="Z44">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.2">
@@ -43357,9 +43336,11 @@
       <c r="W45">
         <v>0</v>
       </c>
-      <c r="Z45">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.2">
@@ -43428,9 +43409,11 @@
       <c r="W46">
         <v>0</v>
       </c>
-      <c r="Z46">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.2">
@@ -43499,9 +43482,11 @@
       <c r="W47">
         <v>0</v>
       </c>
-      <c r="Z47">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.2">
@@ -43570,9 +43555,11 @@
       <c r="W48">
         <v>0</v>
       </c>
-      <c r="Z48">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.2">
@@ -43649,10 +43636,6 @@
       <c r="Y49">
         <v>2</v>
       </c>
-      <c r="Z49">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
@@ -43728,10 +43711,6 @@
       <c r="Y50">
         <v>2</v>
       </c>
-      <c r="Z50">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
@@ -43807,10 +43786,6 @@
       <c r="Y51">
         <v>2</v>
       </c>
-      <c r="Z51">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA51" t="s">
         <v>206</v>
       </c>
@@ -43881,9 +43856,11 @@
       <c r="W52">
         <v>0</v>
       </c>
-      <c r="Z52">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.2">
@@ -43952,9 +43929,11 @@
       <c r="W53">
         <v>0</v>
       </c>
-      <c r="Z53">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.2">
@@ -44023,9 +44002,11 @@
       <c r="W54">
         <v>0</v>
       </c>
-      <c r="Z54">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.2">
@@ -44102,10 +44083,6 @@
       <c r="Y55">
         <v>1</v>
       </c>
-      <c r="Z55">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA55" t="s">
         <v>208</v>
       </c>
@@ -44176,9 +44153,11 @@
       <c r="W56">
         <v>0</v>
       </c>
-      <c r="Z56">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.2">
@@ -44247,9 +44226,11 @@
       <c r="W57">
         <v>0</v>
       </c>
-      <c r="Z57">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X57">
+        <v>1</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.2">
@@ -44318,9 +44299,11 @@
       <c r="W58">
         <v>0</v>
       </c>
-      <c r="Z58">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.2">
@@ -44389,9 +44372,11 @@
       <c r="W59">
         <v>0</v>
       </c>
-      <c r="Z59">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.2">
@@ -44460,9 +44445,11 @@
       <c r="W60">
         <v>0</v>
       </c>
-      <c r="Z60">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.2">
@@ -44531,9 +44518,11 @@
       <c r="W61">
         <v>0</v>
       </c>
-      <c r="Z61">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X61">
+        <v>1</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.2">
@@ -44602,9 +44591,11 @@
       <c r="W62">
         <v>0</v>
       </c>
-      <c r="Z62">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.2">
@@ -44681,10 +44672,6 @@
       <c r="Y63">
         <v>1</v>
       </c>
-      <c r="Z63">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA63" t="s">
         <v>210</v>
       </c>
@@ -44755,9 +44742,11 @@
       <c r="W64">
         <v>0</v>
       </c>
-      <c r="Z64">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X64">
+        <v>1</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.2">
@@ -44826,9 +44815,11 @@
       <c r="W65">
         <v>0</v>
       </c>
-      <c r="Z65">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.2">
@@ -44897,9 +44888,11 @@
       <c r="W66">
         <v>0</v>
       </c>
-      <c r="Z66">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.2">
@@ -44968,9 +44961,11 @@
       <c r="W67">
         <v>0</v>
       </c>
-      <c r="Z67">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.2">
@@ -45039,9 +45034,11 @@
       <c r="W68">
         <v>0</v>
       </c>
-      <c r="Z68">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.2">
@@ -45110,9 +45107,11 @@
       <c r="W69">
         <v>0</v>
       </c>
-      <c r="Z69">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.2">
@@ -45181,9 +45180,11 @@
       <c r="W70">
         <v>0</v>
       </c>
-      <c r="Z70">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.2">
@@ -45252,9 +45253,11 @@
       <c r="W71">
         <v>0</v>
       </c>
-      <c r="Z71">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X71">
+        <v>1</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.2">
@@ -45323,9 +45326,11 @@
       <c r="W72">
         <v>0</v>
       </c>
-      <c r="Z72">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X72">
+        <v>1</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.2">
@@ -45394,9 +45399,11 @@
       <c r="W73">
         <v>0</v>
       </c>
-      <c r="Z73">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.2">
@@ -45465,9 +45472,11 @@
       <c r="W74">
         <v>0</v>
       </c>
-      <c r="Z74">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.2">
@@ -45536,9 +45545,11 @@
       <c r="W75">
         <v>0</v>
       </c>
-      <c r="Z75">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.2">
@@ -45607,9 +45618,11 @@
       <c r="W76">
         <v>0</v>
       </c>
-      <c r="Z76">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.2">
@@ -45686,10 +45699,6 @@
       <c r="Y77">
         <v>3</v>
       </c>
-      <c r="Z77">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
@@ -45757,12 +45766,11 @@
       <c r="W78">
         <v>0</v>
       </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
       <c r="Y78">
         <v>2</v>
-      </c>
-      <c r="Z78">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.2">
@@ -45831,11 +45839,10 @@
       <c r="W79">
         <v>0</v>
       </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
       <c r="Y79">
-        <v>1</v>
-      </c>
-      <c r="Z79">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
         <v>1</v>
       </c>
     </row>
@@ -45913,10 +45920,6 @@
       <c r="Y80">
         <v>2</v>
       </c>
-      <c r="Z80">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA80" t="s">
         <v>213</v>
       </c>
@@ -45987,9 +45990,11 @@
       <c r="W81">
         <v>0</v>
       </c>
-      <c r="Z81">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.2">
@@ -46058,9 +46063,11 @@
       <c r="W82">
         <v>0</v>
       </c>
-      <c r="Z82">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.2">
@@ -46137,10 +46144,6 @@
       <c r="Y83">
         <v>3</v>
       </c>
-      <c r="Z83">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA83" t="s">
         <v>215</v>
       </c>
@@ -46211,9 +46214,11 @@
       <c r="W84">
         <v>0</v>
       </c>
-      <c r="Z84">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X84">
+        <v>1</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.2">
@@ -46290,10 +46295,6 @@
       <c r="Y85">
         <v>2</v>
       </c>
-      <c r="Z85">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
@@ -46369,10 +46370,6 @@
       <c r="Y86">
         <v>2</v>
       </c>
-      <c r="Z86">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
@@ -46440,9 +46437,11 @@
       <c r="W87">
         <v>0</v>
       </c>
-      <c r="Z87">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X87">
+        <v>1</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.2">
@@ -46511,9 +46510,11 @@
       <c r="W88">
         <v>0</v>
       </c>
-      <c r="Z88">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X88">
+        <v>1</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.2">
@@ -46582,9 +46583,11 @@
       <c r="W89">
         <v>0</v>
       </c>
-      <c r="Z89">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.2">
@@ -46653,9 +46656,11 @@
       <c r="W90">
         <v>0</v>
       </c>
-      <c r="Z90">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.2">
@@ -46724,9 +46729,11 @@
       <c r="W91">
         <v>0</v>
       </c>
-      <c r="Z91">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X91">
+        <v>1</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.2">
@@ -46795,9 +46802,11 @@
       <c r="W92">
         <v>0</v>
       </c>
-      <c r="Z92">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.2">
@@ -46866,9 +46875,11 @@
       <c r="W93">
         <v>0</v>
       </c>
-      <c r="Z93">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X93">
+        <v>1</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.2">
@@ -46945,10 +46956,6 @@
       <c r="Y94">
         <v>3</v>
       </c>
-      <c r="Z94">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
       <c r="AA94" t="s">
         <v>219</v>
       </c>
@@ -47019,9 +47026,11 @@
       <c r="W95">
         <v>0</v>
       </c>
-      <c r="Z95">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.2">
@@ -47090,12 +47099,14 @@
       <c r="W96">
         <v>0</v>
       </c>
-      <c r="Z96">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X96">
+        <v>1</v>
+      </c>
+      <c r="Y96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>0</v>
       </c>
@@ -47161,12 +47172,14 @@
       <c r="W97">
         <v>0</v>
       </c>
-      <c r="Z97">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>0</v>
       </c>
@@ -47232,12 +47245,14 @@
       <c r="W98">
         <v>0</v>
       </c>
-      <c r="Z98">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="Y98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -47303,12 +47318,14 @@
       <c r="W99">
         <v>0</v>
       </c>
-      <c r="Z99">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>0</v>
       </c>
@@ -47374,12 +47391,14 @@
       <c r="W100">
         <v>0</v>
       </c>
-      <c r="Z100">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>0</v>
       </c>
@@ -47445,12 +47464,14 @@
       <c r="W101">
         <v>0</v>
       </c>
-      <c r="Z101">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="Y101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -47516,12 +47537,14 @@
       <c r="W102">
         <v>0</v>
       </c>
-      <c r="Z102">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X102">
+        <v>1</v>
+      </c>
+      <c r="Y102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -47587,12 +47610,14 @@
       <c r="W103">
         <v>0</v>
       </c>
-      <c r="Z103">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>0</v>
       </c>
@@ -47658,12 +47683,14 @@
       <c r="W104">
         <v>0</v>
       </c>
-      <c r="Z104">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>0</v>
       </c>
@@ -47729,12 +47756,14 @@
       <c r="W105">
         <v>0</v>
       </c>
-      <c r="Z105">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -47800,12 +47829,14 @@
       <c r="W106">
         <v>0</v>
       </c>
-      <c r="Z106">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X106">
+        <v>1</v>
+      </c>
+      <c r="Y106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>0</v>
       </c>
@@ -47871,12 +47902,14 @@
       <c r="W107">
         <v>0</v>
       </c>
-      <c r="Z107">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>0</v>
       </c>
@@ -47942,12 +47975,14 @@
       <c r="W108">
         <v>0</v>
       </c>
-      <c r="Z108">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X108">
+        <v>1</v>
+      </c>
+      <c r="Y108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>0</v>
       </c>
@@ -48013,12 +48048,14 @@
       <c r="W109">
         <v>0</v>
       </c>
-      <c r="Z109">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X109">
+        <v>1</v>
+      </c>
+      <c r="Y109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>0</v>
       </c>
@@ -48084,12 +48121,14 @@
       <c r="W110">
         <v>0</v>
       </c>
-      <c r="Z110">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X110">
+        <v>1</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>0</v>
       </c>
@@ -48163,12 +48202,8 @@
       <c r="Y111">
         <v>0</v>
       </c>
-      <c r="Z111">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>0</v>
       </c>
@@ -48234,9 +48269,11 @@
       <c r="W112">
         <v>0</v>
       </c>
-      <c r="Z112">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X112">
+        <v>1</v>
+      </c>
+      <c r="Y112">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.2">
@@ -48313,10 +48350,6 @@
       <c r="Y113">
         <v>3</v>
       </c>
-      <c r="Z113">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA113" t="s">
         <v>222</v>
       </c>
@@ -48387,9 +48420,11 @@
       <c r="W114">
         <v>0</v>
       </c>
-      <c r="Z114">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X114">
+        <v>1</v>
+      </c>
+      <c r="Y114">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:27" x14ac:dyDescent="0.2">
@@ -48458,9 +48493,11 @@
       <c r="W115">
         <v>0</v>
       </c>
-      <c r="Z115">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X115">
+        <v>1</v>
+      </c>
+      <c r="Y115">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.2">
@@ -48529,9 +48566,11 @@
       <c r="W116">
         <v>0</v>
       </c>
-      <c r="Z116">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X116">
+        <v>1</v>
+      </c>
+      <c r="Y116">
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.2">
@@ -48600,9 +48639,11 @@
       <c r="W117">
         <v>0</v>
       </c>
-      <c r="Z117">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X117">
+        <v>1</v>
+      </c>
+      <c r="Y117">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.2">
@@ -48671,9 +48712,11 @@
       <c r="W118">
         <v>0</v>
       </c>
-      <c r="Z118">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X118">
+        <v>1</v>
+      </c>
+      <c r="Y118">
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.2">
@@ -48742,9 +48785,11 @@
       <c r="W119">
         <v>0</v>
       </c>
-      <c r="Z119">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X119">
+        <v>1</v>
+      </c>
+      <c r="Y119">
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.2">
@@ -48813,9 +48858,11 @@
       <c r="W120">
         <v>0</v>
       </c>
-      <c r="Z120">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X120">
+        <v>1</v>
+      </c>
+      <c r="Y120">
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.2">
@@ -48884,9 +48931,11 @@
       <c r="W121">
         <v>0</v>
       </c>
-      <c r="Z121">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.2">
@@ -48955,9 +49004,11 @@
       <c r="W122">
         <v>0</v>
       </c>
-      <c r="Z122">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X122">
+        <v>1</v>
+      </c>
+      <c r="Y122">
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.2">
@@ -49026,9 +49077,11 @@
       <c r="W123">
         <v>0</v>
       </c>
-      <c r="Z123">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.2">
@@ -49097,9 +49150,11 @@
       <c r="W124">
         <v>0</v>
       </c>
-      <c r="Z124">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X124">
+        <v>1</v>
+      </c>
+      <c r="Y124">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.2">
@@ -49168,9 +49223,11 @@
       <c r="W125">
         <v>0</v>
       </c>
-      <c r="Z125">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X125">
+        <v>1</v>
+      </c>
+      <c r="Y125">
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.2">
@@ -49239,9 +49296,11 @@
       <c r="W126">
         <v>0</v>
       </c>
-      <c r="Z126">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X126">
+        <v>1</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.2">
@@ -49318,10 +49377,6 @@
       <c r="Y127">
         <v>3</v>
       </c>
-      <c r="Z127">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA127" t="s">
         <v>163</v>
       </c>
@@ -49400,10 +49455,6 @@
       <c r="Y128">
         <v>3</v>
       </c>
-      <c r="Z128">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA128" t="s">
         <v>163</v>
       </c>
@@ -49482,10 +49533,6 @@
       <c r="Y129">
         <v>3</v>
       </c>
-      <c r="Z129">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA129" t="s">
         <v>226</v>
       </c>
@@ -49564,10 +49611,6 @@
       <c r="Y130">
         <v>3</v>
       </c>
-      <c r="Z130">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA130" t="s">
         <v>227</v>
       </c>
@@ -49646,10 +49689,6 @@
       <c r="Y131">
         <v>3</v>
       </c>
-      <c r="Z131">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA131" t="s">
         <v>163</v>
       </c>
@@ -49728,10 +49767,6 @@
       <c r="Y132">
         <v>1</v>
       </c>
-      <c r="Z132">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
@@ -49807,10 +49842,6 @@
       <c r="Y133">
         <v>3</v>
       </c>
-      <c r="Z133">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA133" t="s">
         <v>183</v>
       </c>
@@ -49889,10 +49920,6 @@
       <c r="Y134">
         <v>2</v>
       </c>
-      <c r="Z134">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA134" t="s">
         <v>231</v>
       </c>
@@ -49971,10 +49998,6 @@
       <c r="Y135">
         <v>2</v>
       </c>
-      <c r="Z135">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA135" t="s">
         <v>163</v>
       </c>
@@ -50053,10 +50076,6 @@
       <c r="Y136">
         <v>1</v>
       </c>
-      <c r="Z136">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>2</v>
-      </c>
       <c r="AA136" t="s">
         <v>234</v>
       </c>
@@ -50117,9 +50136,11 @@
       <c r="V137" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="Z137">
-        <f>IF(Tabelle3[[#This Row],[Reflexionstiefe]]="",1,Tabelle3[[#This Row],[Reflexionstiefe]])</f>
-        <v>1</v>
+      <c r="X137">
+        <v>1</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.2">
@@ -50682,11 +50703,11 @@
       </c>
       <c r="W150">
         <f>COUNTIF(Tabelle3[Reflexionstiefe],U150)</f>
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="X150" s="3">
         <f>W150/W$147</f>
-        <v>0.14074074074074075</v>
+        <v>0.79259259259259263</v>
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.2">
@@ -50895,18 +50916,18 @@
         <v>185</v>
       </c>
       <c r="U155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V155" t="s">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="W155">
         <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U155)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X155" s="3">
         <f>W155/W$147</f>
-        <v>5.185185185185185E-2</v>
+        <v>0.11851851851851852</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.2">
@@ -50947,7 +50968,7 @@
         <v>2</v>
       </c>
       <c r="V156" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="W156">
         <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U156)</f>
@@ -50993,18 +51014,18 @@
         <v>1</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V157" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="W157">
         <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U157)</f>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X157" s="3">
         <f>W157/W$147</f>
-        <v>0.11851851851851852</v>
+        <v>5.185185185185185E-2</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.2">
@@ -51040,6 +51061,20 @@
       </c>
       <c r="K158">
         <v>1.5</v>
+      </c>
+      <c r="U158">
+        <v>0</v>
+      </c>
+      <c r="V158" t="s">
+        <v>177</v>
+      </c>
+      <c r="W158">
+        <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U158)</f>
+        <v>100</v>
+      </c>
+      <c r="X158" s="3">
+        <f>W158/W$147</f>
+        <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.2">
